--- a/меню ресторана.xlsx
+++ b/меню ресторана.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t xml:space="preserve">Категория</t>
   </si>
@@ -40,16 +40,64 @@
     <t xml:space="preserve">L</t>
   </si>
   <si>
-    <t xml:space="preserve">Бупгер</t>
+    <t xml:space="preserve">Описание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фото</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бургеры и сэндвичи</t>
   </si>
   <si>
     <t xml:space="preserve">Веганский</t>
   </si>
   <si>
+    <t xml:space="preserve">соевая котлета, томаты свежие, салат айсберг, булочка с кунжутом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://avatars.mds.yandex.net/i?id=05524ab46665a58e1eb3d8d9dabae2ee234ef0bf-16464223-images-thumbs&amp;n=13</t>
+  </si>
+  <si>
     <t xml:space="preserve">Итальянский</t>
   </si>
   <si>
+    <t xml:space="preserve">филе куриное оригинальное, томаты свежие, салат айсберг, булочка с кунжутом, соус «Цезарь» </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 мяса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">филе куриное, говядина, свинина оригинальное, томаты свежие, салат айсберг, булочка с кунжутом, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картофель и закуски</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Морковь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">морковь, специи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картофельные дольки </t>
+  </si>
+  <si>
+    <t xml:space="preserve">картофель специи, соль, растительное масло</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Картофель фри </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Напитки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Апельсиновый сок </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Апельсиновый сок</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кола  </t>
   </si>
 </sst>
 </file>
@@ -59,7 +107,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -82,6 +130,27 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -127,13 +196,37 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -153,64 +246,152 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.2"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="n">
+    </row>
+    <row r="2" customFormat="false" ht="135.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="n">
         <v>123</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <v>433</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="2" t="n">
         <v>777</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="n">
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="57.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>700</v>
       </c>
+      <c r="G3" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="n">
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>800</v>
       </c>
+      <c r="G4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>233</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>180</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" display="https://avatars.mds.yandex.net/i?id=05524ab46665a58e1eb3d8d9dabae2ee234ef0bf-16464223-images-thumbs&amp;n=13"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
